--- a/anthropic/docs/reports/20261022_v0.1.3_對照.xlsx
+++ b/anthropic/docs/reports/20261022_v0.1.3_對照.xlsx
@@ -13123,7 +13123,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>110 列，逐層列來源、單位、2025–2030、低／高、標記；與 TK 對照 2026 P × Q、Q、token 帳；TK token 帳 6.26 倍未閉合屬 Tokenomics 待辦</t>
+          <t>109 列，逐層列來源、單位、2025–2030、低／高、標記；與 TK 對照 2026 P × Q、Q、token 帳；TK token 帳 6.26 倍未閉合屬 Tokenomics 待辦</t>
         </is>
       </c>
     </row>
